--- a/storage/app/template/list_of_applicant_top_ranking.xlsx
+++ b/storage/app/template/list_of_applicant_top_ranking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\RSP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650A2B32-FAEF-4B2C-BA18-794095350ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB76E1E-5C61-43E0-82FB-12294EB67CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8113A99E-9156-40D8-A2D8-36A56E68640F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>NAME</t>
   </si>
@@ -60,7 +60,16 @@
     <t>Plantilla Item No</t>
   </si>
   <si>
-    <t>Remarks</t>
+    <t>OFFICE</t>
+  </si>
+  <si>
+    <t>POSITION</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>LENGTH OG SERVICE</t>
   </si>
 </sst>
 </file>
@@ -507,7 +516,7 @@
     <col min="3" max="3" width="42.28515625" style="2" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="22.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" style="1" customWidth="1"/>
     <col min="7" max="7" width="15" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.5703125" style="1" customWidth="1"/>
     <col min="9" max="9" width="39.28515625" style="2" customWidth="1"/>
@@ -655,9 +664,15 @@
       <c r="C10" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
+      <c r="D10" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>11</v>
+      </c>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>

--- a/storage/app/template/list_of_applicant_top_ranking.xlsx
+++ b/storage/app/template/list_of_applicant_top_ranking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\RSP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB76E1E-5C61-43E0-82FB-12294EB67CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4189BAB9-05F1-407A-84AE-1D81B6137B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8113A99E-9156-40D8-A2D8-36A56E68640F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>NAME</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>LENGTH OG SERVICE</t>
+  </si>
+  <si>
+    <t>SG</t>
   </si>
 </sst>
 </file>
@@ -517,7 +520,7 @@
     <col min="4" max="4" width="13.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="22.28515625" style="1" customWidth="1"/>
     <col min="6" max="6" width="22.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.5703125" style="1" customWidth="1"/>
     <col min="9" max="9" width="39.28515625" style="2" customWidth="1"/>
     <col min="10" max="10" width="19.140625" style="1" customWidth="1"/>
@@ -668,12 +671,14 @@
         <v>9</v>
       </c>
       <c r="E10" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="G10" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
